--- a/examples/reports/MRB_Report_Clifford_Fidelity_Model.xlsx
+++ b/examples/reports/MRB_Report_Clifford_Fidelity_Model.xlsx
@@ -166,7 +166,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="13335000" cy="8943975"/>
+    <ext cx="16116300" cy="10410825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -196,7 +196,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="13506450" cy="8943975"/>
+    <ext cx="16116300" cy="10410825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -226,7 +226,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="13163550" cy="8943975"/>
+    <ext cx="16116300" cy="10410825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -256,7 +256,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10134600" cy="8934450"/>
+    <ext cx="15020925" cy="10763250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -566,13 +566,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -646,7 +646,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Key Results</t>
+          <t>Analysis Results</t>
         </is>
       </c>
     </row>
@@ -658,17 +658,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Process Fidelity</t>
+          <t>Qubit Group</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>State Fidelity</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>EPC</t>
+          <t>EPC Error</t>
         </is>
       </c>
     </row>
@@ -678,10 +678,20 @@
           <t>MRB Decay Fit (0)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n">
-        <v>0.001826234989561804</v>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>1.959e-02</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>9.28e-05</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -690,10 +700,20 @@
           <t>MRB Decay Fit (1)</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n">
-        <v>0.001959932336254799</v>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>1.976e-02</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>8.05e-05</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -702,21 +722,21 @@
           <t>MRB Decay Fit ((0, 1))</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n">
-        <v>0.02713001968420348</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>MRB Direct Polarization</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2.948e-02</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>1.22e-04</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
